--- a/ibiden/dist/20261025_Ibiden模型_v0.2.xlsx
+++ b/ibiden/dist/20261025_Ibiden模型_v0.2.xlsx
@@ -8099,7 +8099,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8355,7 +8355,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8476,7 +8476,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8597,7 +8597,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8718,7 +8718,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8839,7 +8839,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
